--- a/backtest_runs/20260410_193731/by_symbol/UNIC/UNIC.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/UNIC/UNIC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-1517.080000000003</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>100461.72</v>
@@ -679,7 +679,7 @@
         <v>-6002.360000000001</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>94459.36</v>
@@ -955,7 +955,7 @@
         <v>-857.4800000000051</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>107189.64</v>
@@ -1001,7 +1001,7 @@
         <v>-923.439999999992</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>106266.2</v>
@@ -1093,7 +1093,7 @@
         <v>-13192</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>93799.76000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-2638.400000000002</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>92942.28</v>
@@ -1277,7 +1277,7 @@
         <v>-857.4800000000051</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>94393.40000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-1583.040000000001</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>92810.36</v>
@@ -1369,7 +1369,7 @@
         <v>-263.8399999999943</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>92546.52</v>
@@ -1415,7 +1415,7 @@
         <v>-1319.200000000007</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>91227.32000000001</v>
@@ -1461,7 +1461,7 @@
         <v>-527.6800000000005</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>90699.64</v>
@@ -1507,7 +1507,7 @@
         <v>-65.95999999999859</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>90633.68000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-1055.360000000001</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>92678.44</v>
